--- a/artfynd/A 5795-2025 artfynd.xlsx
+++ b/artfynd/A 5795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97072944</v>
+        <v>97073236</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373276.1044745092</v>
+        <v>373304</v>
       </c>
       <c r="R2" t="n">
-        <v>6935123.221132591</v>
+        <v>6935275</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2021-11-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,12 +776,7 @@
         <v>97072987</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373276.4521091118</v>
+        <v>373276</v>
       </c>
       <c r="R3" t="n">
-        <v>6935095.940554155</v>
+        <v>6935096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2021-11-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +871,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97073132</v>
+        <v>97072862</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>373249.1335422563</v>
+        <v>373312</v>
       </c>
       <c r="R4" t="n">
-        <v>6935192.648678605</v>
+        <v>6935120</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2021-11-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97073236</v>
+        <v>97072996</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373304.1318950502</v>
+        <v>373276</v>
       </c>
       <c r="R5" t="n">
-        <v>6935275.584130594</v>
+        <v>6935096</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2021-11-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,19 +1067,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97072996</v>
+        <v>97073132</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373276.4521091118</v>
+        <v>373250</v>
       </c>
       <c r="R6" t="n">
-        <v>6935095.940554155</v>
+        <v>6935193</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2021-11-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,458 +1162,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>97073134</v>
-      </c>
-      <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Härjedalen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>373249.1335422563</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6935192.648678605</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>97072735</v>
-      </c>
-      <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Härjedalen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>373411.3308603569</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6935173.984900953</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>97072862</v>
-      </c>
-      <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Härjedalen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>373312.099080867</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6935120.461559589</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>97072710</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Härjedalen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>373492.5135190469</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6935239.750945988</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5795-2025 artfynd.xlsx
+++ b/artfynd/A 5795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97073236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97072987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97072862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97072996</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97073132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>